--- a/testcases/discount-optimization/discount-optimization-exemption.xlsx
+++ b/testcases/discount-optimization/discount-optimization-exemption.xlsx
@@ -790,7 +790,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TC-DOP-EXM-010</t>
+          <t>TC-DOP-EXM-003</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -974,7 +974,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TC-DOP-EXM-011</t>
+          <t>TC-DOP-EXM-004</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TC-DOP-EXM-020</t>
+          <t>TC-DOP-EXM-005</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TC-DOP-EXM-021</t>
+          <t>TC-DOP-EXM-006</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
